--- a/simulation_data.xlsx
+++ b/simulation_data.xlsx
@@ -1,21 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hitesh\OneDrive\Desktop\Durve Sir\SpectraSoft\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F9A63FC-8AC2-453A-9A84-49B34295BF57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30305"/>
+  <workbookPr/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB51FDAE-D952-4C3C-97D9-A330881BC18B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{87C041A7-4E0C-4D04-89D5-86DD14720B30}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="LO" sheetId="1" r:id="rId1"/>
+    <sheet name="README" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,15 +23,133 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+  <si>
+    <t>ITG</t>
+  </si>
+  <si>
+    <t>ELE</t>
+  </si>
+  <si>
+    <t>SAMPLE1</t>
+  </si>
+  <si>
+    <t>SAMPLE2</t>
+  </si>
+  <si>
+    <t>SAMPLE3</t>
+  </si>
+  <si>
+    <t>SAMPLE4</t>
+  </si>
+  <si>
+    <t>FE</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>MN1</t>
+  </si>
+  <si>
+    <t>MN2</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>NI1</t>
+  </si>
+  <si>
+    <t>NI2</t>
+  </si>
+  <si>
+    <t>CR1</t>
+  </si>
+  <si>
+    <t>CR2</t>
+  </si>
+  <si>
+    <t>MO</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
+    <t>NB</t>
+  </si>
+  <si>
+    <t>CU</t>
+  </si>
+  <si>
+    <t>TI</t>
+  </si>
+  <si>
+    <t>SpectraSoft Simulation Workbook</t>
+  </si>
+  <si>
+    <t>Analytical Group sheet</t>
+  </si>
+  <si>
+    <t>LO</t>
+  </si>
+  <si>
+    <t>Matching rule</t>
+  </si>
+  <si>
+    <t>Selected Analytical Group name must exactly match the sheet name.</t>
+  </si>
+  <si>
+    <t>Unique channel key</t>
+  </si>
+  <si>
+    <t>ELE column</t>
+  </si>
+  <si>
+    <t>Human-readable validation only; software maps ITG through Page 3.</t>
+  </si>
+  <si>
+    <t>Sample selection</t>
+  </si>
+  <si>
+    <t>Job sample name selects the matching sample column; e.g. SAMPLE2.</t>
+  </si>
+  <si>
+    <t>Data type</t>
+  </si>
+  <si>
+    <t>Synthetic normalized/pre-correction intensity values for testing only.</t>
+  </si>
+  <si>
+    <t>Important</t>
+  </si>
+  <si>
+    <t>These are synthetic values, not certified spectrometer measurements.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -43,13 +157,51 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF666666"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF008000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF666666"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F7FA"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -64,14 +216,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -81,6 +256,21 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LOSimulationData" displayName="LOSimulationData" ref="A1:F17">
+  <autoFilter ref="A1:F17" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ITG"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ELE"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="SAMPLE1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="SAMPLE2"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SAMPLE3"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="SAMPLE4"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -94,44 +284,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -158,32 +348,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -210,24 +382,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -239,150 +393,629 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{B5DE6E61-7327-4710-AF04-DB19AD01FD4F}">
+  <we:reference id="df76232d-21a6-4463-9d19-0518ac5aab5d" version="1.1.0.0" store="excatalog" storeType="excatalog"/>
+  <we:alternateReferences>
+    <we:reference id="WA200000556" version="1.1.0.0" store="en-gb" storeType="omex"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="documentId" value="&quot;0d839ee0-db39-4ac4-85d4-ea93101716d5&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27803CCF-F21B-44B0-9C65-B87997CD62A0}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="6" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="24" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0.85099999999999998</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0.84699999999999998</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0.85399999999999998</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0.84899999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0.121</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.24199999999999999</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.245</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0.24099999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0.54100000000000004</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0.53300000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.312</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.308</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.316</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.311</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="5">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="D7" s="5">
+        <v>6.2E-2</v>
+      </c>
+      <c r="E7" s="5">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="F7" s="5">
+        <v>6.3E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3">
+        <v>4.7E-2</v>
+      </c>
+      <c r="D8" s="3">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="E8" s="3">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="F8" s="3">
+        <v>4.5999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="D9" s="5">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0.38600000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0.20300000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0.46200000000000002</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0.27600000000000002</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0.27400000000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0.13300000000000001</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0.129</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0.13200000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="3">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="D14" s="3">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="E14" s="3">
+        <v>9.4E-2</v>
+      </c>
+      <c r="F14" s="3">
+        <v>9.0999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="4">
+        <v>15</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="5">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="D15" s="5">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="E15" s="5">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="F15" s="5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="2">
+        <v>16</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0.154</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0.157</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.153</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="4">
+        <v>17</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0.108</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0.105</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0.111</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0.107</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="90" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="9"/>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>